--- a/observation/config_observations.xlsx
+++ b/observation/config_observations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6. calibration.py\observation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74134CF-DEF4-4BBF-A79F-48A07DA7197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28561D1A-7EA3-48C8-9EF6-BD51362F41E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
   <si>
     <t>catchment</t>
   </si>
@@ -69,15 +69,6 @@
     <t>baseflow_minderhoutlocal.xlsx</t>
   </si>
   <si>
-    <t>flow_minderhouttotal_fixed.xlsx</t>
-  </si>
-  <si>
-    <t>baseflow_minderhouttotal_fixed.xlsx</t>
-  </si>
-  <si>
-    <t>quickflow_minderhouttotal_fixed.xlsx</t>
-  </si>
-  <si>
     <t>catchment_size_m2</t>
   </si>
   <si>
@@ -118,6 +109,33 @@
   </si>
   <si>
     <t>quickflow_filename</t>
+  </si>
+  <si>
+    <t>flow_minderhout_fixed.xlsx</t>
+  </si>
+  <si>
+    <t>baseflow_minderhout_fixed.xlsx</t>
+  </si>
+  <si>
+    <t>quickflow_minderhout_fixed.xlsx</t>
+  </si>
+  <si>
+    <t>Greenvale</t>
+  </si>
+  <si>
+    <t>Rainfall_Station_X.xlsx</t>
+  </si>
+  <si>
+    <t>ETp_Station_X.xlsx</t>
+  </si>
+  <si>
+    <t>Flow_Station_Y.xlsx</t>
+  </si>
+  <si>
+    <t>Quickflow_Station_Y.xlsx</t>
+  </si>
+  <si>
+    <t>Baseflow_Station_Y.xlsx</t>
   </si>
 </sst>
 </file>
@@ -453,14 +471,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -476,42 +494,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2">
         <v>93298161.637540698</v>
@@ -529,19 +547,19 @@
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>2</v>
@@ -549,7 +567,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2">
         <v>55925385.298757903</v>
@@ -587,7 +605,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2">
         <v>37372776.338782802</v>
@@ -620,10 +638,49 @@
         <v>7</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1">
+        <v>300000000</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>